--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.06885181650131</v>
+        <v>12.36118842018146</v>
       </c>
       <c r="D2" t="n">
-        <v>76.03339108224834</v>
+        <v>12.35542605086536</v>
       </c>
       <c r="E2" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F2" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.064846494336</v>
+        <v>10.2480375553296</v>
       </c>
       <c r="D3" t="n">
-        <v>62.87572294583066</v>
+        <v>10.21730497869748</v>
       </c>
       <c r="E3" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F3" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.1810951868111</v>
+        <v>7.179427967856804</v>
       </c>
       <c r="D4" t="n">
-        <v>43.55430298943027</v>
+        <v>7.077574235782419</v>
       </c>
       <c r="E4" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F4" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.30448359271689</v>
+        <v>4.924478583816495</v>
       </c>
       <c r="D5" t="n">
-        <v>29.6808235856654</v>
+        <v>4.823133832670629</v>
       </c>
       <c r="E5" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F5" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.17121336371205</v>
+        <v>5.390322171603208</v>
       </c>
       <c r="D6" t="n">
-        <v>33.83761372759392</v>
+        <v>5.498612230734012</v>
       </c>
       <c r="E6" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F6" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>81.55119990245899</v>
+        <v>13.25206998414959</v>
       </c>
       <c r="D7" t="n">
-        <v>81.25001521381854</v>
+        <v>13.20312747224551</v>
       </c>
       <c r="E7" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F7" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.72801077307469</v>
+        <v>10.35580175062464</v>
       </c>
       <c r="D8" t="n">
-        <v>63.88456910260914</v>
+        <v>10.38124247917399</v>
       </c>
       <c r="E8" t="n">
-        <v>18.84658254680741</v>
+        <v>3.062569663856205</v>
       </c>
       <c r="F8" t="n">
-        <v>18.84901014149759</v>
+        <v>3.062964147993359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
